--- a/output/intraday/riepilogo_intraday_2026-05-06.xlsx
+++ b/output/intraday/riepilogo_intraday_2026-05-06.xlsx
@@ -802,7 +802,7 @@
         <v>46147</v>
       </c>
       <c r="C2" t="n">
-        <v>42.02</v>
+        <v>43.7</v>
       </c>
       <c r="D2" t="n">
         <v>3280000</v>
@@ -815,7 +815,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-23.08%</t>
+          <t>-23.98%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -1036,7 +1036,7 @@
         <v>46147</v>
       </c>
       <c r="C3" t="n">
-        <v>60.78</v>
+        <v>59.36</v>
       </c>
       <c r="D3" t="n">
         <v>13480000</v>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-30.11%</t>
+          <t>-29.49%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -1270,7 +1270,7 @@
         <v>46147</v>
       </c>
       <c r="C4" t="n">
-        <v>31.07</v>
+        <v>30.66</v>
       </c>
       <c r="D4" t="n">
         <v>842590000</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>24.39%</t>
+          <t>24.78%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1504,7 +1504,7 @@
         <v>46147</v>
       </c>
       <c r="C5" t="n">
-        <v>40.69</v>
+        <v>39.31</v>
       </c>
       <c r="D5" t="n">
         <v>2360000</v>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>3.47%</t>
         </is>
       </c>
       <c r="H5" t="n">

--- a/output/intraday/riepilogo_intraday_2026-05-06.xlsx
+++ b/output/intraday/riepilogo_intraday_2026-05-06.xlsx
@@ -843,7 +843,7 @@
         <v>1.32</v>
       </c>
       <c r="P2" t="n">
-        <v>23583596</v>
+        <v>47426315</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>1.59</v>
       </c>
       <c r="AI2" t="n">
-        <v>7160607</v>
+        <v>7160535</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.68</v>
@@ -942,7 +942,7 @@
         <v>1.53</v>
       </c>
       <c r="AU2" t="n">
-        <v>14301143</v>
+        <v>38143852</v>
       </c>
       <c r="AV2" t="n">
         <v>1.71</v>
@@ -954,7 +954,7 @@
         <v>1.53</v>
       </c>
       <c r="AY2" t="n">
-        <v>16501000</v>
+        <v>40343709</v>
       </c>
       <c r="AZ2" t="n">
         <v>1.61</v>
@@ -966,7 +966,7 @@
         <v>1.53</v>
       </c>
       <c r="BC2" t="n">
-        <v>17619490</v>
+        <v>41462199</v>
       </c>
       <c r="BD2" t="n">
         <v>1.58</v>
@@ -978,7 +978,7 @@
         <v>1.53</v>
       </c>
       <c r="BG2" t="n">
-        <v>20513159</v>
+        <v>44355868</v>
       </c>
       <c r="BH2" t="n">
         <v>1.59</v>
@@ -1077,7 +1077,7 @@
         <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>17485563</v>
+        <v>17485763</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>3.94</v>
       </c>
       <c r="AI3" t="n">
-        <v>3849052</v>
+        <v>3849252</v>
       </c>
       <c r="AJ3" t="n">
         <v>4.15</v>
@@ -1152,7 +1152,7 @@
         <v>3.94</v>
       </c>
       <c r="AM3" t="n">
-        <v>6176951</v>
+        <v>6177151</v>
       </c>
       <c r="AN3" t="n">
         <v>3.94</v>
@@ -1164,7 +1164,7 @@
         <v>3.43</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8971754</v>
+        <v>8971954</v>
       </c>
       <c r="AR3" t="n">
         <v>3.49</v>
@@ -1176,7 +1176,7 @@
         <v>3.17</v>
       </c>
       <c r="AU3" t="n">
-        <v>10591199</v>
+        <v>10591399</v>
       </c>
       <c r="AV3" t="n">
         <v>3.3</v>
@@ -1188,7 +1188,7 @@
         <v>3.17</v>
       </c>
       <c r="AY3" t="n">
-        <v>11866546</v>
+        <v>11866746</v>
       </c>
       <c r="AZ3" t="n">
         <v>3.39</v>
@@ -1200,7 +1200,7 @@
         <v>3.17</v>
       </c>
       <c r="BC3" t="n">
-        <v>12895805</v>
+        <v>12896005</v>
       </c>
       <c r="BD3" t="n">
         <v>3.41</v>
@@ -1212,7 +1212,7 @@
         <v>3.17</v>
       </c>
       <c r="BG3" t="n">
-        <v>14885857</v>
+        <v>14886057</v>
       </c>
       <c r="BH3" t="n">
         <v>3.58</v>
@@ -1311,7 +1311,7 @@
         <v>23.85</v>
       </c>
       <c r="P4" t="n">
-        <v>6103402</v>
+        <v>6104888</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>18.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>206231</v>
+        <v>206181</v>
       </c>
       <c r="AB4" t="n">
         <v>20.25</v>
@@ -1398,7 +1398,7 @@
         <v>18.15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1611016</v>
+        <v>1611040</v>
       </c>
       <c r="AR4" t="n">
         <v>21.62</v>
@@ -1410,7 +1410,7 @@
         <v>18.15</v>
       </c>
       <c r="AU4" t="n">
-        <v>1871291</v>
+        <v>1871315</v>
       </c>
       <c r="AV4" t="n">
         <v>21.55</v>
@@ -1422,7 +1422,7 @@
         <v>18.15</v>
       </c>
       <c r="AY4" t="n">
-        <v>2441087</v>
+        <v>2441153</v>
       </c>
       <c r="AZ4" t="n">
         <v>21.53</v>
@@ -1434,7 +1434,7 @@
         <v>18.15</v>
       </c>
       <c r="BC4" t="n">
-        <v>2759595</v>
+        <v>2759661</v>
       </c>
       <c r="BD4" t="n">
         <v>22.18</v>
@@ -1446,7 +1446,7 @@
         <v>18.15</v>
       </c>
       <c r="BG4" t="n">
-        <v>3978952</v>
+        <v>3980316</v>
       </c>
       <c r="BH4" t="n">
         <v>22.61</v>
@@ -1545,7 +1545,7 @@
         <v>2.11</v>
       </c>
       <c r="P5" t="n">
-        <v>24964063</v>
+        <v>60049979</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>1.82</v>
       </c>
       <c r="BC5" t="n">
-        <v>3613622</v>
+        <v>3613834</v>
       </c>
       <c r="BD5" t="n">
         <v>2</v>
@@ -1680,7 +1680,7 @@
         <v>1.82</v>
       </c>
       <c r="BG5" t="n">
-        <v>18464017</v>
+        <v>53549933</v>
       </c>
       <c r="BH5" t="n">
         <v>2.29</v>

--- a/output/intraday/riepilogo_intraday_2026-05-06.xlsx
+++ b/output/intraday/riepilogo_intraday_2026-05-06.xlsx
@@ -831,7 +831,7 @@
         <v>1.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="M2" t="n">
         <v>1.87</v>
@@ -843,7 +843,7 @@
         <v>1.32</v>
       </c>
       <c r="P2" t="n">
-        <v>47426315</v>
+        <v>23583596</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>1.59</v>
       </c>
       <c r="AI2" t="n">
-        <v>7160535</v>
+        <v>7160607</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.68</v>
@@ -942,7 +942,7 @@
         <v>1.53</v>
       </c>
       <c r="AU2" t="n">
-        <v>38143852</v>
+        <v>14301143</v>
       </c>
       <c r="AV2" t="n">
         <v>1.71</v>
@@ -954,7 +954,7 @@
         <v>1.53</v>
       </c>
       <c r="AY2" t="n">
-        <v>40343709</v>
+        <v>16501000</v>
       </c>
       <c r="AZ2" t="n">
         <v>1.61</v>
@@ -966,7 +966,7 @@
         <v>1.53</v>
       </c>
       <c r="BC2" t="n">
-        <v>41462199</v>
+        <v>17619490</v>
       </c>
       <c r="BD2" t="n">
         <v>1.58</v>
@@ -978,7 +978,7 @@
         <v>1.53</v>
       </c>
       <c r="BG2" t="n">
-        <v>44355868</v>
+        <v>20513159</v>
       </c>
       <c r="BH2" t="n">
         <v>1.59</v>
@@ -1065,7 +1065,7 @@
         <v>4.55</v>
       </c>
       <c r="L3" t="n">
-        <v>4.51</v>
+        <v>4.54</v>
       </c>
       <c r="M3" t="n">
         <v>4.7</v>
@@ -1077,7 +1077,7 @@
         <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>17485763</v>
+        <v>17485563</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>3.94</v>
       </c>
       <c r="AI3" t="n">
-        <v>3849252</v>
+        <v>3849052</v>
       </c>
       <c r="AJ3" t="n">
         <v>4.15</v>
@@ -1152,7 +1152,7 @@
         <v>3.94</v>
       </c>
       <c r="AM3" t="n">
-        <v>6177151</v>
+        <v>6176951</v>
       </c>
       <c r="AN3" t="n">
         <v>3.94</v>
@@ -1164,7 +1164,7 @@
         <v>3.43</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8971954</v>
+        <v>8971754</v>
       </c>
       <c r="AR3" t="n">
         <v>3.49</v>
@@ -1176,7 +1176,7 @@
         <v>3.17</v>
       </c>
       <c r="AU3" t="n">
-        <v>10591399</v>
+        <v>10591199</v>
       </c>
       <c r="AV3" t="n">
         <v>3.3</v>
@@ -1188,7 +1188,7 @@
         <v>3.17</v>
       </c>
       <c r="AY3" t="n">
-        <v>11866746</v>
+        <v>11866546</v>
       </c>
       <c r="AZ3" t="n">
         <v>3.39</v>
@@ -1200,7 +1200,7 @@
         <v>3.17</v>
       </c>
       <c r="BC3" t="n">
-        <v>12896005</v>
+        <v>12895805</v>
       </c>
       <c r="BD3" t="n">
         <v>3.41</v>
@@ -1212,7 +1212,7 @@
         <v>3.17</v>
       </c>
       <c r="BG3" t="n">
-        <v>14886057</v>
+        <v>14885857</v>
       </c>
       <c r="BH3" t="n">
         <v>3.58</v>
@@ -1299,7 +1299,7 @@
         <v>18.59</v>
       </c>
       <c r="L4" t="n">
-        <v>19.15</v>
+        <v>18.46</v>
       </c>
       <c r="M4" t="n">
         <v>23.97</v>
@@ -1311,7 +1311,7 @@
         <v>23.85</v>
       </c>
       <c r="P4" t="n">
-        <v>6104888</v>
+        <v>6103402</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>18.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>206181</v>
+        <v>206231</v>
       </c>
       <c r="AB4" t="n">
         <v>20.25</v>
@@ -1398,7 +1398,7 @@
         <v>18.15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1611040</v>
+        <v>1611016</v>
       </c>
       <c r="AR4" t="n">
         <v>21.62</v>
@@ -1410,7 +1410,7 @@
         <v>18.15</v>
       </c>
       <c r="AU4" t="n">
-        <v>1871315</v>
+        <v>1871291</v>
       </c>
       <c r="AV4" t="n">
         <v>21.55</v>
@@ -1422,7 +1422,7 @@
         <v>18.15</v>
       </c>
       <c r="AY4" t="n">
-        <v>2441153</v>
+        <v>2441087</v>
       </c>
       <c r="AZ4" t="n">
         <v>21.53</v>
@@ -1434,7 +1434,7 @@
         <v>18.15</v>
       </c>
       <c r="BC4" t="n">
-        <v>2759661</v>
+        <v>2759595</v>
       </c>
       <c r="BD4" t="n">
         <v>22.18</v>
@@ -1446,7 +1446,7 @@
         <v>18.15</v>
       </c>
       <c r="BG4" t="n">
-        <v>3980316</v>
+        <v>3978952</v>
       </c>
       <c r="BH4" t="n">
         <v>22.61</v>
@@ -1533,7 +1533,7 @@
         <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
         <v>2.56</v>
@@ -1545,7 +1545,7 @@
         <v>2.11</v>
       </c>
       <c r="P5" t="n">
-        <v>60049979</v>
+        <v>24964063</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>1.82</v>
       </c>
       <c r="BC5" t="n">
-        <v>3613834</v>
+        <v>3613622</v>
       </c>
       <c r="BD5" t="n">
         <v>2</v>
@@ -1680,7 +1680,7 @@
         <v>1.82</v>
       </c>
       <c r="BG5" t="n">
-        <v>53549933</v>
+        <v>18464017</v>
       </c>
       <c r="BH5" t="n">
         <v>2.29</v>
